--- a/Assets/Excel/AIConfig.xlsx
+++ b/Assets/Excel/AIConfig.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>EnemyId</t>
   </si>
@@ -68,7 +68,7 @@
     <t>巡逻</t>
   </si>
   <si>
-    <t>Walking</t>
+    <t>Moving</t>
   </si>
   <si>
     <t>待机</t>
@@ -77,6 +77,15 @@
     <t>Idle</t>
   </si>
   <si>
+    <t>追击</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>Attack_Combo_01_01</t>
+  </si>
+  <si>
     <t>From</t>
   </si>
   <si>
@@ -113,10 +122,16 @@
     <t>Arrive</t>
   </si>
   <si>
-    <t>Timer</t>
+    <t>Timer;NoTarget</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>OnAnimEnd</t>
+  </si>
+  <si>
+    <t>Timer;HasTarget</t>
   </si>
 </sst>
 </file>
@@ -1089,8 +1104,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="4" width="40" customWidth="1"/>
   </cols>
@@ -1163,6 +1178,34 @@
       </c>
       <c r="D5" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2001</v>
+      </c>
+      <c r="B6">
+        <v>2003</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2001</v>
+      </c>
+      <c r="B7">
+        <v>2004</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1174,8 +1217,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="36.9" customWidth="1"/>
@@ -1189,19 +1232,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1218,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
         <v>4</v>
@@ -1229,19 +1272,19 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1255,7 +1298,7 @@
         <v>2001</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1272,13 +1315,67 @@
         <v>2002</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>2001</v>
+      </c>
+      <c r="B6">
+        <v>2003</v>
+      </c>
+      <c r="C6">
+        <v>2004</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>2001</v>
+      </c>
+      <c r="B7">
+        <v>2004</v>
+      </c>
+      <c r="C7">
+        <v>2001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>2001</v>
+      </c>
+      <c r="B8">
+        <v>2001</v>
+      </c>
+      <c r="C8">
+        <v>2003</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
